--- a/PASTA EXCEL VINI.xlsx
+++ b/PASTA EXCEL VINI.xlsx
@@ -5,15 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48FEFC46-2D51-4E5A-9D16-B8B13D597C55}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{297592B4-9D16-4317-AFF0-7C109F394517}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{C52650C3-E84F-455B-82FE-53EBBECABF85}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" activeTab="3" xr2:uid="{C52650C3-E84F-455B-82FE-53EBBECABF85}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha2" sheetId="2" r:id="rId2"/>
+    <sheet name="Planilha3" sheetId="3" r:id="rId3"/>
+    <sheet name="Planilha4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
   <si>
     <t>JANEIRO</t>
   </si>
@@ -79,6 +82,120 @@
   </si>
   <si>
     <t>SALDO</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>NOME</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>HELENA</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>EDSON</t>
+  </si>
+  <si>
+    <t>ELISANGELA</t>
+  </si>
+  <si>
+    <t>REGINA</t>
+  </si>
+  <si>
+    <t>PAULO</t>
+  </si>
+  <si>
+    <t>SALARIO BRUTO</t>
+  </si>
+  <si>
+    <t>GRATIFICAÇÃO</t>
+  </si>
+  <si>
+    <t>INSS</t>
+  </si>
+  <si>
+    <t>GRATIFICAÇÃO R$</t>
+  </si>
+  <si>
+    <t>INSS R$</t>
+  </si>
+  <si>
+    <t>SALARIO LIQUIDO</t>
+  </si>
+  <si>
+    <t>Valor do dolar</t>
+  </si>
+  <si>
+    <t>Produtos</t>
+  </si>
+  <si>
+    <t>Qtde</t>
+  </si>
+  <si>
+    <t>Total R$</t>
+  </si>
+  <si>
+    <t>Total US$</t>
+  </si>
+  <si>
+    <t>Papelaria Papel Branco</t>
+  </si>
+  <si>
+    <t>Caneta Azul</t>
+  </si>
+  <si>
+    <t>Caneta Vermelha</t>
+  </si>
+  <si>
+    <t>Caderno</t>
+  </si>
+  <si>
+    <t>Régua</t>
+  </si>
+  <si>
+    <t>Lápis</t>
+  </si>
+  <si>
+    <t>Papel Sulfite</t>
+  </si>
+  <si>
+    <t>Tinta Nanquim</t>
+  </si>
+  <si>
+    <t>Preço Unit.</t>
+  </si>
+  <si>
+    <t>Receita Bruta</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jan-Mar</t>
+  </si>
+  <si>
+    <t>Abr-Jun</t>
+  </si>
+  <si>
+    <t>Jul-Set</t>
+  </si>
+  <si>
+    <t>Out-Dez</t>
+  </si>
+  <si>
+    <t>Total do Ano</t>
+  </si>
+  <si>
+    <t>Projeção para o ano de 2003</t>
+  </si>
+  <si>
+    <t>Despesa liquida</t>
   </si>
 </sst>
 </file>
@@ -89,7 +206,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,6 +215,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -122,19 +247,35 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -704,27 +845,27 @@
         <v>16</v>
       </c>
       <c r="B14" s="3">
-        <f>SUM(B5:B12)</f>
+        <f t="shared" ref="B14:G14" si="0">SUM(B5:B12)</f>
         <v>725</v>
       </c>
       <c r="C14" s="3">
-        <f>SUM(C5:C12)</f>
+        <f t="shared" si="0"/>
         <v>735</v>
       </c>
       <c r="D14" s="3">
-        <f>SUM(D5:D12)</f>
+        <f t="shared" si="0"/>
         <v>763</v>
       </c>
       <c r="E14" s="3">
-        <f>SUM(E5:E12)</f>
+        <f t="shared" si="0"/>
         <v>837</v>
       </c>
       <c r="F14" s="3">
-        <f>SUM(F5:F12)</f>
+        <f t="shared" si="0"/>
         <v>641</v>
       </c>
       <c r="G14" s="3">
-        <f>SUM(G5:G12)</f>
+        <f t="shared" si="0"/>
         <v>758</v>
       </c>
     </row>
@@ -733,31 +874,658 @@
         <v>17</v>
       </c>
       <c r="B16" s="3">
-        <f>B2-B14</f>
+        <f t="shared" ref="B16:G16" si="1">B2-B14</f>
         <v>-225</v>
       </c>
       <c r="C16" s="3">
-        <f>C2-C14</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="D16" s="3">
-        <f>D2-D14</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="E16" s="3">
-        <f>E2-E14</f>
+        <f t="shared" si="1"/>
         <v>-137</v>
       </c>
       <c r="F16" s="3">
-        <f>F2-F14</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="G16" s="3">
-        <f>G2-G14</f>
+        <f t="shared" si="1"/>
         <v>-58</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78F82B23-BDA6-4579-8ADF-46A4AE0CA4A1}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2">
+        <v>853</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="F2" s="3">
+        <f t="shared" ref="F2:F9" si="0">C2*D2</f>
+        <v>85.300000000000011</v>
+      </c>
+      <c r="G2" s="3">
+        <f t="shared" ref="G2:G9" si="1">C2*E2</f>
+        <v>76.77</v>
+      </c>
+      <c r="H2" s="3">
+        <f>SUM(C2,G2)-F2</f>
+        <v>844.47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="2">
+        <v>951</v>
+      </c>
+      <c r="D3" s="5">
+        <v>9.9900000000000003E-2</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="F3" s="3">
+        <f t="shared" si="0"/>
+        <v>95.004900000000006</v>
+      </c>
+      <c r="G3" s="3">
+        <f t="shared" si="1"/>
+        <v>76.08</v>
+      </c>
+      <c r="H3" s="3">
+        <f>SUM(C3,G3)-F3</f>
+        <v>932.07509999999991</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2">
+        <v>456</v>
+      </c>
+      <c r="D4" s="5">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0.06</v>
+      </c>
+      <c r="F4" s="3">
+        <f t="shared" si="0"/>
+        <v>39.398400000000002</v>
+      </c>
+      <c r="G4" s="3">
+        <f t="shared" si="1"/>
+        <v>27.36</v>
+      </c>
+      <c r="H4" s="3">
+        <f>SUM(C4,G4)-F4</f>
+        <v>443.96160000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="2">
+        <v>500</v>
+      </c>
+      <c r="D5" s="5">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.06</v>
+      </c>
+      <c r="F5" s="3">
+        <f t="shared" si="0"/>
+        <v>42.5</v>
+      </c>
+      <c r="G5" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="H5" s="3">
+        <f>SUM(C5,G50-F5)</f>
+        <v>457.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2">
+        <v>850</v>
+      </c>
+      <c r="D6" s="5">
+        <v>8.9899999999999994E-2</v>
+      </c>
+      <c r="E6" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F6" s="3">
+        <f t="shared" si="0"/>
+        <v>76.414999999999992</v>
+      </c>
+      <c r="G6" s="3">
+        <f t="shared" si="1"/>
+        <v>59.500000000000007</v>
+      </c>
+      <c r="H6" s="3">
+        <f>SUM(C6,G6)-F6</f>
+        <v>833.08500000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="2">
+        <v>459</v>
+      </c>
+      <c r="D7" s="5">
+        <v>6.25E-2</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="F7" s="3">
+        <f t="shared" si="0"/>
+        <v>28.6875</v>
+      </c>
+      <c r="G7" s="3">
+        <f t="shared" si="1"/>
+        <v>22.950000000000003</v>
+      </c>
+      <c r="H7" s="3">
+        <f>SUM(C7,G7)-F6</f>
+        <v>405.53499999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="2">
+        <v>478</v>
+      </c>
+      <c r="D8" s="5">
+        <v>7.1199999999999999E-2</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="F8" s="3">
+        <f t="shared" si="0"/>
+        <v>34.0336</v>
+      </c>
+      <c r="G8" s="3">
+        <f t="shared" si="1"/>
+        <v>23.900000000000002</v>
+      </c>
+      <c r="H8" s="3">
+        <f>SUM(C8,G8)-F8</f>
+        <v>467.8664</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="2">
+        <v>658</v>
+      </c>
+      <c r="D9" s="5">
+        <v>5.9900000000000002E-2</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="F9" s="3">
+        <f t="shared" si="0"/>
+        <v>39.414200000000001</v>
+      </c>
+      <c r="G9" s="3">
+        <f t="shared" si="1"/>
+        <v>26.32</v>
+      </c>
+      <c r="H9" s="3">
+        <f>SUM(C9,G9)-F9</f>
+        <v>644.9058</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C1F19A3-6C25-436E-9936-B81402BF96D6}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="2">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4">
+        <v>500</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="D4" s="7">
+        <f>B4*C4</f>
+        <v>75</v>
+      </c>
+      <c r="E4">
+        <f>D4/$B$1</f>
+        <v>25.510204081632654</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5">
+        <v>750</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="D5" s="7">
+        <f t="shared" ref="D5:D10" si="0">B5*C5</f>
+        <v>112.5</v>
+      </c>
+      <c r="E5">
+        <f t="shared" ref="E5:E10" si="1">D5/$B$1</f>
+        <v>38.265306122448983</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6">
+        <v>250</v>
+      </c>
+      <c r="C6" s="1">
+        <v>10</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="0"/>
+        <v>2500</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>850.34013605442181</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7">
+        <v>310</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="7">
+        <f t="shared" si="0"/>
+        <v>155</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>52.721088435374149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8">
+        <v>500</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>17.006802721088437</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9">
+        <v>1500</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="D9" s="7">
+        <f t="shared" si="0"/>
+        <v>3750</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>1275.5102040816328</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10">
+        <v>190</v>
+      </c>
+      <c r="C10" s="1">
+        <v>6</v>
+      </c>
+      <c r="D10" s="7">
+        <f t="shared" si="0"/>
+        <v>1140</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>387.75510204081633</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC7319B7-3111-4263-B06F-C43BA340FEDF}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="11">
+        <v>140000</v>
+      </c>
+      <c r="C4" s="11">
+        <v>185000</v>
+      </c>
+      <c r="D4" s="11">
+        <v>204100</v>
+      </c>
+      <c r="E4" s="11">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="11">
+        <v>20000</v>
+      </c>
+      <c r="C7" s="11">
+        <v>26000</v>
+      </c>
+      <c r="D7" s="11">
+        <v>33800</v>
+      </c>
+      <c r="E7" s="11">
+        <v>43940</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="11">
+        <v>20000</v>
+      </c>
+      <c r="C8" s="11">
+        <v>15600</v>
+      </c>
+      <c r="D8" s="11">
+        <v>20280</v>
+      </c>
+      <c r="E8" s="11">
+        <v>26364</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="11">
+        <v>12000</v>
+      </c>
+      <c r="C9" s="11">
+        <v>20930</v>
+      </c>
+      <c r="D9" s="11">
+        <v>27209</v>
+      </c>
+      <c r="E9" s="11">
+        <v>35371</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="11">
+        <v>16100</v>
+      </c>
+      <c r="C10" s="11">
+        <v>28870</v>
+      </c>
+      <c r="D10" s="11">
+        <v>33631</v>
+      </c>
+      <c r="E10" s="11">
+        <v>43720.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="11">
+        <v>19900</v>
+      </c>
+      <c r="C11" s="11">
+        <v>39000</v>
+      </c>
+      <c r="D11" s="11">
+        <v>50700</v>
+      </c>
+      <c r="E11" s="11">
+        <v>65910</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="11">
+        <v>25000</v>
+      </c>
+      <c r="C12" s="11">
+        <v>32500</v>
+      </c>
+      <c r="D12" s="11">
+        <v>42250</v>
+      </c>
+      <c r="E12" s="11">
+        <v>54925</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/PASTA EXCEL VINI.xlsx
+++ b/PASTA EXCEL VINI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{297592B4-9D16-4317-AFF0-7C109F394517}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAFECE30-EB51-471E-A7CA-065ED2163350}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" activeTab="3" xr2:uid="{C52650C3-E84F-455B-82FE-53EBBECABF85}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="3" xr2:uid="{C52650C3-E84F-455B-82FE-53EBBECABF85}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="71">
   <si>
     <t>JANEIRO</t>
   </si>
@@ -196,6 +196,51 @@
   </si>
   <si>
     <t>Despesa liquida</t>
+  </si>
+  <si>
+    <t>Coluna1</t>
+  </si>
+  <si>
+    <t>Coluna2</t>
+  </si>
+  <si>
+    <t>Coluna3</t>
+  </si>
+  <si>
+    <t>Coluna4</t>
+  </si>
+  <si>
+    <t>Coluna5</t>
+  </si>
+  <si>
+    <t>Salarios</t>
+  </si>
+  <si>
+    <t>Juros</t>
+  </si>
+  <si>
+    <t>Aluguel</t>
+  </si>
+  <si>
+    <t>Propaganda</t>
+  </si>
+  <si>
+    <t>Suprimentos</t>
+  </si>
+  <si>
+    <t>Diversos</t>
+  </si>
+  <si>
+    <t>Total do Trim.</t>
+  </si>
+  <si>
+    <t>Receita Liquida</t>
+  </si>
+  <si>
+    <t>Situação</t>
+  </si>
+  <si>
+    <t>Valor acumulado do ano de despesas</t>
   </si>
 </sst>
 </file>
@@ -264,20 +309,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -288,6 +355,24 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7F4AE42D-6A53-4321-A428-1BCD0BEAB5BD}" name="Tabela1" displayName="Tabela1" ref="A1:E11" totalsRowShown="0">
+  <autoFilter ref="A1:E11" xr:uid="{7D5198AA-6C06-4866-A75B-96E050217347}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{468885FA-AD89-4634-9E5C-0E03D28D9294}" name="Coluna1"/>
+    <tableColumn id="2" xr3:uid="{D6AA279A-5E05-42C2-AA99-6C06124D7CDC}" name="Coluna2"/>
+    <tableColumn id="3" xr3:uid="{DE489171-4620-420D-942F-B90259BF60F6}" name="Coluna3" dataDxfId="1" dataCellStyle="Moeda"/>
+    <tableColumn id="4" xr3:uid="{F267D49D-5E9C-41D1-8D24-E762B858D117}" name="Coluna4" dataDxfId="0">
+      <calculatedColumnFormula>B2*C2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{BAE8C02A-D451-4721-943E-9F2F2CCCF029}" name="Coluna5">
+      <calculatedColumnFormula>D2/$B$2</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1181,208 +1266,229 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C1F19A3-6C25-436E-9936-B81402BF96D6}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" customWidth="1"/>
     <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B2" s="2">
         <v>2.94</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" t="s">
-        <v>38</v>
-      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4">
-        <v>500</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="D4" s="7">
-        <f>B4*C4</f>
-        <v>75</v>
-      </c>
-      <c r="E4">
-        <f>D4/$B$1</f>
-        <v>25.510204081632654</v>
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="C5" s="1">
         <v>0.15</v>
       </c>
       <c r="D5" s="7">
-        <f t="shared" ref="D5:D10" si="0">B5*C5</f>
-        <v>112.5</v>
+        <f>B5*C5</f>
+        <v>75</v>
       </c>
       <c r="E5">
-        <f t="shared" ref="E5:E10" si="1">D5/$B$1</f>
-        <v>38.265306122448983</v>
+        <f>D5/$B$2</f>
+        <v>25.510204081632654</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="C6" s="1">
-        <v>10</v>
+        <v>0.15</v>
       </c>
       <c r="D6" s="7">
-        <f t="shared" si="0"/>
-        <v>2500</v>
+        <f t="shared" ref="D6:D11" si="0">B6*C6</f>
+        <v>112.5</v>
       </c>
       <c r="E6">
-        <f t="shared" si="1"/>
-        <v>850.34013605442181</v>
+        <f>D6/$B$2</f>
+        <v>38.265306122448983</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="C7" s="1">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>155</v>
+        <v>2500</v>
       </c>
       <c r="E7">
-        <f t="shared" si="1"/>
-        <v>52.721088435374149</v>
+        <f>D7/$B$2</f>
+        <v>850.34013605442181</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="C8" s="1">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="E8">
-        <f t="shared" si="1"/>
-        <v>17.006802721088437</v>
+        <f>D8/$B$2</f>
+        <v>52.721088435374149</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="C9" s="1">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>3750</v>
+        <v>50</v>
       </c>
       <c r="E9">
-        <f t="shared" si="1"/>
-        <v>1275.5102040816328</v>
+        <f>D9/$B$2</f>
+        <v>17.006802721088437</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10">
+        <v>1500</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="D10" s="7">
+        <f t="shared" si="0"/>
+        <v>3750</v>
+      </c>
+      <c r="E10">
+        <f>D10/$B$2</f>
+        <v>1275.5102040816328</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>46</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>190</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D11" s="7">
         <f t="shared" si="0"/>
         <v>1140</v>
       </c>
-      <c r="E10">
-        <f t="shared" si="1"/>
+      <c r="E11">
+        <f>D11/$B$2</f>
         <v>387.75510204081633</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
-  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC7319B7-3111-4263-B06F-C43BA340FEDF}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -1405,17 +1511,21 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="11">
+      <c r="B4" s="9">
         <v>140000</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="9">
         <v>185000</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="9">
         <v>204100</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="9">
         <v>240000</v>
+      </c>
+      <c r="F4" s="9">
+        <f>SUM(B4,C4,D4,E4)</f>
+        <v>769100</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1439,87 +1549,213 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="11">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="9">
         <v>20000</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="9">
         <v>26000</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="9">
         <v>33800</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <v>43940</v>
       </c>
+      <c r="F7" s="9">
+        <f>SUM(B7:E7)</f>
+        <v>123740</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="11">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="9">
         <v>20000</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="9">
         <v>15600</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="9">
         <v>20280</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <v>26364</v>
       </c>
+      <c r="F8" s="9">
+        <f t="shared" ref="F8:F12" si="0">SUM(B8:E8)</f>
+        <v>82244</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="11">
+      <c r="A9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="9">
         <v>12000</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="9">
         <v>20930</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="9">
         <v>27209</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="9">
         <v>35371</v>
       </c>
+      <c r="F9" s="9">
+        <f t="shared" si="0"/>
+        <v>95510</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="11">
+      <c r="A10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="9">
         <v>16100</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="9">
         <v>28870</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="9">
         <v>33631</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="9">
         <v>43720.3</v>
       </c>
+      <c r="F10" s="9">
+        <f t="shared" si="0"/>
+        <v>122321.3</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="11">
+      <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="9">
         <v>19900</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="9">
         <v>39000</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="9">
         <v>50700</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="9">
         <v>65910</v>
       </c>
+      <c r="F11" s="9">
+        <f t="shared" si="0"/>
+        <v>175510</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="11">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="9">
         <v>25000</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="9">
         <v>32500</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="9">
         <v>42250</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="9">
         <v>54925</v>
+      </c>
+      <c r="F12" s="9">
+        <f t="shared" si="0"/>
+        <v>154675</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="9">
+        <f>SUM(B7:B12)</f>
+        <v>113000</v>
+      </c>
+      <c r="C14" s="9">
+        <f>SUM(C7:C12)</f>
+        <v>162900</v>
+      </c>
+      <c r="D14" s="9">
+        <f>SUM(D7:D12)</f>
+        <v>207870</v>
+      </c>
+      <c r="E14" s="9">
+        <f>SUM(E7:E12)</f>
+        <v>270230.3</v>
+      </c>
+      <c r="F14" s="9">
+        <f>SUM(F7:F12)</f>
+        <v>754000.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="9">
+        <f>B4-B14</f>
+        <v>27000</v>
+      </c>
+      <c r="C15" s="9">
+        <f>C4-C14</f>
+        <v>22100</v>
+      </c>
+      <c r="D15" s="9">
+        <f>D4-D14</f>
+        <v>-3770</v>
+      </c>
+      <c r="E15" s="9">
+        <f>E4-E14</f>
+        <v>-30230.299999999988</v>
+      </c>
+      <c r="F15" s="9">
+        <f>F4-F14</f>
+        <v>15099.699999999953</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="str">
+        <f>IF(B15&lt;1000,"Prejuízo Total",IF(B15&lt;=5000,"Lucro Médio",IF(B15&gt;5000,"Lucro Total")))</f>
+        <v>Lucro Total</v>
+      </c>
+      <c r="C16" t="str">
+        <f>IF(C15&lt;1000,"Prejuízo Total",IF(C15&lt;=5000,"Lucro Médio",IF(C15&gt;5000,"Lucro Total")))</f>
+        <v>Lucro Total</v>
+      </c>
+      <c r="D16" t="str">
+        <f>IF(D15&lt;1000,"Prejuízo Total",IF(D15&lt;=5000,"Lucro Médio",IF(D15&gt;5000,"Lucro Total")))</f>
+        <v>Prejuízo Total</v>
+      </c>
+      <c r="E16" t="str">
+        <f>IF(E15&lt;1000,"Prejuízo Total",IF(E15&lt;=5000,"Lucro Médio",IF(E15&gt;5000,"Lucro Total")))</f>
+        <v>Prejuízo Total</v>
+      </c>
+      <c r="F16" t="str">
+        <f>IF(F15&lt;1000,"Prejuízo Total",IF(F15&lt;=5000,"Lucro Médio",IF(F15&gt;5000,"Lucro Total")))</f>
+        <v>Lucro Total</v>
+      </c>
+    </row>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="9">
+        <f>SUM(F7:F12)</f>
+        <v>754000.3</v>
       </c>
     </row>
   </sheetData>
